--- a/结果/问题三_中继部署方案_修复版.xlsx
+++ b/结果/问题三_中继部署方案_修复版.xlsx
@@ -73,25 +73,25 @@
     <t>R02</t>
   </si>
   <si>
-    <t>S011</t>
-  </si>
-  <si>
-    <t>S001</t>
+    <t>S003,S005,S007,S008,S009,S015</t>
+  </si>
+  <si>
+    <t>S002,S004,S009,S010,S012,S013,S014</t>
   </si>
   <si>
     <t>RE-01,RE-02</t>
   </si>
   <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 1.3128768013485503, "energy_kwh": 0.025163472025847212}, {"component_id": "RE-01", "phase": "hover", "start_min": 4.81287680134855, "end_min": 143.0766874181205, "energy_kwh": 2.534836527974153}, {"component_id": "RE-02", "phase": "hover", "start_min": 143.0766874181205, "end_min": 210.4276706856699, "energy_kwh": 1.2347680265717393}, {"component_id": "RE-02", "phase": "return", "start_min": 210.42767068566994, "end_min": 216.7405474870185, "energy_kwh": 0.025163472025847212}]</t>
-  </si>
-  <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 1.506797383946659, "energy_kwh": 0.028880283192310965}, {"component_id": "RE-01", "phase": "hover", "start_min": 5.006797383946659, "end_min": 143.06787284618426, "energy_kwh": 2.5311197168076895}, {"component_id": "RE-02", "phase": "hover", "start_min": 143.06787284618426, "end_min": 210.62159126826805, "energy_kwh": 1.238484837738203}, {"component_id": "RE-02", "phase": "return", "start_min": 210.62159126826805, "end_min": 217.1283886522147, "energy_kwh": 0.028880283192310965}]</t>
-  </si>
-  <si>
-    <t>{"RE-01": [143.0766874181205, 173.0766874181205], "RE-02": [216.7405474870185, 246.7405474870185]}</t>
-  </si>
-  <si>
-    <t>{"RE-01": [143.06787284618426, 173.06787284618426], "RE-02": [217.1283886522147, 247.1283886522147]}</t>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295948, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295948, "end_min": 213.98774278104838, "energy_kwh": 1.3021282277316297}, {"component_id": "RE-02", "phase": "return", "start_min": 213.98774278104835, "end_min": 222.81127487594068, "energy_kwh": 0.07328436515210275}]</t>
+  </si>
+  <si>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 189.5492509213889, "energy_kwh": 0.856240995935087}, {"component_id": "RE-02", "phase": "return", "start_min": 189.5492509213889, "end_min": 200.95492577293726, "energy_kwh": 0.12277543465467701}]</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.96256672295948, 172.96256672295948], "RE-02": [222.81127487594068, 252.81127487594068]}</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [200.95492577293726, 230.95492577293726]}</t>
   </si>
 </sst>
 </file>
@@ -510,25 +510,25 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>109.2262272</v>
+        <v>109.207295298</v>
       </c>
       <c r="C2">
-        <v>23.017840972</v>
+        <v>23.030100736</v>
       </c>
       <c r="D2">
-        <v>456.7368123214927</v>
+        <v>663.2882416244034</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>4.81287680134855</v>
+        <v>7.323532094892318</v>
       </c>
       <c r="G2">
-        <v>210.4276706856699</v>
+        <v>213.9877427810484</v>
       </c>
       <c r="H2">
-        <v>216.7405474870185</v>
+        <v>222.8112748759407</v>
       </c>
       <c r="I2">
         <v>205.6147938843214</v>
@@ -537,13 +537,13 @@
         <v>19</v>
       </c>
       <c r="K2">
-        <v>3.819931498597587</v>
+        <v>3.935412592883733</v>
       </c>
       <c r="L2">
-        <v>0.05032694405169442</v>
+        <v>0.1465687303042055</v>
       </c>
       <c r="M2">
-        <v>3.769604554545892</v>
+        <v>3.788843862579527</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -563,25 +563,25 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>109.238848468</v>
+        <v>109.276712272</v>
       </c>
       <c r="C3">
-        <v>23.017840972</v>
+        <v>23.038273912</v>
       </c>
       <c r="D3">
-        <v>451.9746633002158</v>
+        <v>653.5848184328352</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>5.006797383946659</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="G3">
-        <v>210.621591268268</v>
+        <v>189.5492509213889</v>
       </c>
       <c r="H3">
-        <v>217.1283886522147</v>
+        <v>200.9549257729373</v>
       </c>
       <c r="I3">
         <v>205.6147938843214</v>
@@ -590,13 +590,13 @@
         <v>20</v>
       </c>
       <c r="K3">
-        <v>3.827365120930514</v>
+        <v>3.539016430589764</v>
       </c>
       <c r="L3">
-        <v>0.05776056638462193</v>
+        <v>0.245550869309354</v>
       </c>
       <c r="M3">
-        <v>3.769604554545892</v>
+        <v>3.29346556128041</v>
       </c>
       <c r="N3">
         <v>2</v>

--- a/结果/问题三_中继部署方案_修复版.xlsx
+++ b/结果/问题三_中继部署方案_修复版.xlsx
@@ -82,16 +82,16 @@
     <t>RE-01,RE-02</t>
   </si>
   <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295948, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295948, "end_min": 213.98774278104838, "energy_kwh": 1.3021282277316297}, {"component_id": "RE-02", "phase": "return", "start_min": 213.98774278104835, "end_min": 222.81127487594068, "energy_kwh": 0.07328436515210275}]</t>
-  </si>
-  <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 189.5492509213889, "energy_kwh": 0.856240995935087}, {"component_id": "RE-02", "phase": "return", "start_min": 189.5492509213889, "end_min": 200.95492577293726, "energy_kwh": 0.12277543465467701}]</t>
-  </si>
-  <si>
-    <t>{"RE-01": [142.96256672295948, 172.96256672295948], "RE-02": [222.81127487594068, 252.81127487594068]}</t>
-  </si>
-  <si>
-    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [200.95492577293726, 230.95492577293726]}</t>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295945, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295945, "end_min": 182.2643138933139, "energy_kwh": 0.7205320314564982}, {"component_id": "RE-02", "phase": "return", "start_min": 182.2643138933139, "end_min": 191.08784598820623, "energy_kwh": 0.07328436515210275}]</t>
+  </si>
+  <si>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 182.02506583457242, "energy_kwh": 0.7182976026767847}, {"component_id": "RE-02", "phase": "return", "start_min": 182.02506583457242, "end_min": 193.43074068612077, "energy_kwh": 0.12277543465467701}]</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.96256672295945, 172.96256672295945], "RE-02": [191.08784598820623, 221.08784598820623]}</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [193.43074068612077, 223.43074068612077]}</t>
   </si>
 </sst>
 </file>
@@ -525,25 +525,25 @@
         <v>7.323532094892318</v>
       </c>
       <c r="G2">
-        <v>213.9877427810484</v>
+        <v>182.2643138933139</v>
       </c>
       <c r="H2">
-        <v>222.8112748759407</v>
+        <v>191.0878459882062</v>
       </c>
       <c r="I2">
-        <v>205.6147938843214</v>
+        <v>173.6387822549022</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2">
-        <v>3.935412592883733</v>
+        <v>3.353816396608601</v>
       </c>
       <c r="L2">
         <v>0.1465687303042055</v>
       </c>
       <c r="M2">
-        <v>3.788843862579527</v>
+        <v>3.207247666304396</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -578,25 +578,25 @@
         <v>9.905674851548365</v>
       </c>
       <c r="G3">
-        <v>189.5492509213889</v>
+        <v>182.0250658345724</v>
       </c>
       <c r="H3">
-        <v>200.9549257729373</v>
+        <v>193.4307406861208</v>
       </c>
       <c r="I3">
-        <v>205.6147938843214</v>
+        <v>173.6387822549022</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
       </c>
       <c r="K3">
-        <v>3.539016430589764</v>
+        <v>3.401073037331462</v>
       </c>
       <c r="L3">
         <v>0.245550869309354</v>
       </c>
       <c r="M3">
-        <v>3.29346556128041</v>
+        <v>3.155522168022108</v>
       </c>
       <c r="N3">
         <v>2</v>

--- a/结果/问题三_中继部署方案_修复版.xlsx
+++ b/结果/问题三_中继部署方案_修复版.xlsx
@@ -82,16 +82,16 @@
     <t>RE-01,RE-02</t>
   </si>
   <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295945, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295945, "end_min": 182.2643138933139, "energy_kwh": 0.7205320314564982}, {"component_id": "RE-02", "phase": "return", "start_min": 182.2643138933139, "end_min": 191.08784598820623, "energy_kwh": 0.07328436515210275}]</t>
-  </si>
-  <si>
-    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 182.02506583457242, "energy_kwh": 0.7182976026767847}, {"component_id": "RE-02", "phase": "return", "start_min": 182.02506583457242, "end_min": 193.43074068612077, "energy_kwh": 0.12277543465467701}]</t>
-  </si>
-  <si>
-    <t>{"RE-01": [142.96256672295945, 172.96256672295945], "RE-02": [191.08784598820623, 221.08784598820623]}</t>
-  </si>
-  <si>
-    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [193.43074068612077, 223.43074068612077]}</t>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 3.8235320948923186, "energy_kwh": 0.07328436515210275}, {"component_id": "RE-01", "phase": "hover", "start_min": 7.323532094892318, "end_min": 142.96256672295945, "energy_kwh": 2.4867156348478976}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.96256672295945, "end_min": 178.29339143974642, "energy_kwh": 0.6477317864744276}, {"component_id": "RE-02", "phase": "return", "start_min": 178.29339143974642, "end_min": 187.11692353463874, "energy_kwh": 0.07328436515210275}]</t>
+  </si>
+  <si>
+    <t>[{"component_id": "RE-01", "phase": "outbound", "start_min": 0.0, "end_min": 6.405674851548366, "energy_kwh": 0.12277543465467701}, {"component_id": "RE-01", "phase": "hover", "start_min": 9.905674851548365, "end_min": 142.8451965976569, "energy_kwh": 2.4372245653453235}, {"component_id": "RE-02", "phase": "hover", "start_min": 142.8451965976569, "end_min": 177.38426100259625, "energy_kwh": 0.6332161807572216}, {"component_id": "RE-02", "phase": "return", "start_min": 177.38426100259625, "end_min": 188.7899358541446, "energy_kwh": 0.12277543465467701}]</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.96256672295945, 172.96256672295945], "RE-02": [187.11692353463874, 217.11692353463874]}</t>
+  </si>
+  <si>
+    <t>{"RE-01": [142.8451965976569, 172.8451965976569], "RE-02": [188.7899358541446, 218.7899358541446]}</t>
   </si>
 </sst>
 </file>
@@ -525,25 +525,25 @@
         <v>7.323532094892318</v>
       </c>
       <c r="G2">
-        <v>182.2643138933139</v>
+        <v>178.2933914397464</v>
       </c>
       <c r="H2">
-        <v>191.0878459882062</v>
+        <v>187.1169235346387</v>
       </c>
       <c r="I2">
-        <v>173.6387822549022</v>
+        <v>169.7573716381891</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2">
-        <v>3.353816396608601</v>
+        <v>3.281016151626531</v>
       </c>
       <c r="L2">
         <v>0.1465687303042055</v>
       </c>
       <c r="M2">
-        <v>3.207247666304396</v>
+        <v>3.134447421322325</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -578,25 +578,25 @@
         <v>9.905674851548365</v>
       </c>
       <c r="G3">
-        <v>182.0250658345724</v>
+        <v>177.3842610025962</v>
       </c>
       <c r="H3">
-        <v>193.4307406861208</v>
+        <v>188.7899358541446</v>
       </c>
       <c r="I3">
-        <v>173.6387822549022</v>
+        <v>169.7573716381891</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
       </c>
       <c r="K3">
-        <v>3.401073037331462</v>
+        <v>3.315991615411899</v>
       </c>
       <c r="L3">
         <v>0.245550869309354</v>
       </c>
       <c r="M3">
-        <v>3.155522168022108</v>
+        <v>3.070440746102545</v>
       </c>
       <c r="N3">
         <v>2</v>
